--- a/NewRepoInfo.xlsx
+++ b/NewRepoInfo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wjiang25\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\00.Work\00.GitData\R_Repo_Factory_202603\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD8937A-1E32-4CF2-9E91-CD42B7E7DD26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDBE5581-4D7B-4EEC-B110-87238D16B47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C9434CED-3E06-4E35-AD4B-02AAE4ABB6B6}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -153,10 +153,6 @@
   </si>
   <si>
     <t>RO3234567</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>STD-3333</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -654,7 +650,7 @@
         <v>13</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H4" s="6" t="str" cm="1">
         <f t="array" ref="H4">IF(B4&lt;&gt;"","AEGIS-"&amp;_xlfn.SWITCH(C4,"DEV","ZDEV","VAL","ZVAL","PRD","PRD","?")&amp;"-"&amp;_xlfn.SWITCH(D4,"Study","S","Molecule","M","?")&amp;"-"&amp;E4&amp;"-"&amp;_xlfn.SWITCH(D4,"Study",F4&amp;"-","Molecule","","?")&amp;G4,"")</f>
@@ -681,7 +677,7 @@
         <v>17</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H5" s="6" t="str" cm="1">
         <f t="array" ref="H5">IF(B5&lt;&gt;"","AEGIS-"&amp;_xlfn.SWITCH(C5,"DEV","ZDEV","VAL","ZVAL","PRD","PRD","?")&amp;"-"&amp;_xlfn.SWITCH(D5,"Study","S","Molecule","M","?")&amp;"-"&amp;E5&amp;"-"&amp;_xlfn.SWITCH(D5,"Study",F5&amp;"-","Molecule","","?")&amp;G5,"")</f>
@@ -704,22 +700,22 @@
       <c r="E6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="F6" s="5"/>
       <c r="G6" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H6" s="6" t="str" cm="1">
         <f t="array" ref="H6">IF(B6&lt;&gt;"","AEGIS-"&amp;_xlfn.SWITCH(C6,"DEV","ZDEV","VAL","ZVAL","PRD","PRD","?")&amp;"-"&amp;_xlfn.SWITCH(D6,"Study","S","Molecule","M","?")&amp;"-"&amp;E6&amp;"-"&amp;_xlfn.SWITCH(D6,"Study",F6&amp;"-","Molecule","","?")&amp;G6,"")</f>
-        <v>AEGIS-PRD-S-RO3234567-STD-3333-ReportingEvent-33</v>
+        <v>AEGIS-PRD-S-RO3234567--ReportingEvent-33</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4">
         <v>4</v>
       </c>
-      <c r="B7" s="5"/>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="5"/>
@@ -727,7 +723,7 @@
       <c r="G7" s="5"/>
       <c r="H7" s="6" t="str" cm="1">
         <f t="array" ref="H7">IF(B7&lt;&gt;"","AEGIS-"&amp;_xlfn.SWITCH(C7,"DEV","ZDEV","VAL","ZVAL","PRD","PRD","?")&amp;"-"&amp;_xlfn.SWITCH(D7,"Study","S","Molecule","M","?")&amp;"-"&amp;E7&amp;"-"&amp;_xlfn.SWITCH(D7,"Study",F7&amp;"-","Molecule","","?")&amp;G7,"")</f>
-        <v/>
+        <v>AEGIS-?-?--?</v>
       </c>
     </row>
     <row r="8" spans="1:8">

--- a/NewRepoInfo.xlsx
+++ b/NewRepoInfo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\00.Work\00.GitData\R_Repo_Factory_202603\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDBE5581-4D7B-4EEC-B110-87238D16B47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F388420A-534F-45A7-ADE7-87D7AF85ABB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C9434CED-3E06-4E35-AD4B-02AAE4ABB6B6}"/>
   </bookViews>
@@ -170,7 +170,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,6 +184,13 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -233,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -255,6 +262,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -599,8 +609,8 @@
         <v>14</v>
       </c>
       <c r="H2" s="6" t="str" cm="1">
-        <f t="array" ref="H2">IF(B2&lt;&gt;"","AEGIS-"&amp;_xlfn.SWITCH(C2,"DEV","ZDEV","VAL","ZVAL","PRD","PRD","?")&amp;"-"&amp;_xlfn.SWITCH(D2,"Study","S","Molecule","M","?")&amp;"-"&amp;E2&amp;"-"&amp;_xlfn.SWITCH(D2,"Study",F2&amp;"-","Molecule","","?")&amp;G2,"")</f>
-        <v>AEGIS-ZDEV-S-RO1234567-STD-0001-ReportingEvent-01</v>
+        <f t="array" ref="H2">IF(B2&lt;&gt;"","AEGIS-"&amp;C2&amp;"-"&amp;_xlfn.SWITCH(D2,"Study","S","Molecule","M","?")&amp;"-"&amp;E2&amp;"-"&amp;_xlfn.SWITCH(D2,"Study",F2&amp;"-","Molecule","","?")&amp;G2,"")</f>
+        <v>AEGIS-DEV-S-RO1234567-STD-0001-ReportingEvent-01</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -626,7 +636,7 @@
         <v>18</v>
       </c>
       <c r="H3" s="6" t="str" cm="1">
-        <f t="array" ref="H3">IF(B3&lt;&gt;"","AEGIS-"&amp;_xlfn.SWITCH(C3,"DEV","ZDEV","VAL","ZVAL","PRD","PRD","?")&amp;"-"&amp;_xlfn.SWITCH(D3,"Study","S","Molecule","M","?")&amp;"-"&amp;E3&amp;"-"&amp;_xlfn.SWITCH(D3,"Study",F3&amp;"-","Molecule","","?")&amp;G3,"")</f>
+        <f t="array" ref="H3">IF(B3&lt;&gt;"","AEGIS-"&amp;C3&amp;"-"&amp;_xlfn.SWITCH(D3,"Study","S","Molecule","M","?")&amp;"-"&amp;E3&amp;"-"&amp;_xlfn.SWITCH(D3,"Study",F3&amp;"-","Molecule","","?")&amp;G3,"")</f>
         <v>AEGIS-PRD-M-RO1234567-ReportingEvent-02</v>
       </c>
     </row>
@@ -653,8 +663,8 @@
         <v>23</v>
       </c>
       <c r="H4" s="6" t="str" cm="1">
-        <f t="array" ref="H4">IF(B4&lt;&gt;"","AEGIS-"&amp;_xlfn.SWITCH(C4,"DEV","ZDEV","VAL","ZVAL","PRD","PRD","?")&amp;"-"&amp;_xlfn.SWITCH(D4,"Study","S","Molecule","M","?")&amp;"-"&amp;E4&amp;"-"&amp;_xlfn.SWITCH(D4,"Study",F4&amp;"-","Molecule","","?")&amp;G4,"")</f>
-        <v>AEGIS-ZDEV-S-RO1234567-STD-0001-ReportingEvent-31</v>
+        <f t="array" ref="H4">IF(B4&lt;&gt;"","AEGIS-"&amp;C4&amp;"-"&amp;_xlfn.SWITCH(D4,"Study","S","Molecule","M","?")&amp;"-"&amp;E4&amp;"-"&amp;_xlfn.SWITCH(D4,"Study",F4&amp;"-","Molecule","","?")&amp;G4,"")</f>
+        <v>AEGIS-DEV-S-RO1234567-STD-0001-ReportingEvent-31</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -680,8 +690,8 @@
         <v>24</v>
       </c>
       <c r="H5" s="6" t="str" cm="1">
-        <f t="array" ref="H5">IF(B5&lt;&gt;"","AEGIS-"&amp;_xlfn.SWITCH(C5,"DEV","ZDEV","VAL","ZVAL","PRD","PRD","?")&amp;"-"&amp;_xlfn.SWITCH(D5,"Study","S","Molecule","M","?")&amp;"-"&amp;E5&amp;"-"&amp;_xlfn.SWITCH(D5,"Study",F5&amp;"-","Molecule","","?")&amp;G5,"")</f>
-        <v>AEGIS-ZVAL-M-RO2234567-ReportingEvent-32</v>
+        <f t="array" ref="H5">IF(B5&lt;&gt;"","AEGIS-"&amp;C5&amp;"-"&amp;_xlfn.SWITCH(D5,"Study","S","Molecule","M","?")&amp;"-"&amp;E5&amp;"-"&amp;_xlfn.SWITCH(D5,"Study",F5&amp;"-","Molecule","","?")&amp;G5,"")</f>
+        <v>AEGIS-VAL-M-RO2234567-ReportingEvent-32</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -705,7 +715,7 @@
         <v>25</v>
       </c>
       <c r="H6" s="6" t="str" cm="1">
-        <f t="array" ref="H6">IF(B6&lt;&gt;"","AEGIS-"&amp;_xlfn.SWITCH(C6,"DEV","ZDEV","VAL","ZVAL","PRD","PRD","?")&amp;"-"&amp;_xlfn.SWITCH(D6,"Study","S","Molecule","M","?")&amp;"-"&amp;E6&amp;"-"&amp;_xlfn.SWITCH(D6,"Study",F6&amp;"-","Molecule","","?")&amp;G6,"")</f>
+        <f t="array" ref="H6">IF(B6&lt;&gt;"","AEGIS-"&amp;C6&amp;"-"&amp;_xlfn.SWITCH(D6,"Study","S","Molecule","M","?")&amp;"-"&amp;E6&amp;"-"&amp;_xlfn.SWITCH(D6,"Study",F6&amp;"-","Molecule","","?")&amp;G6,"")</f>
         <v>AEGIS-PRD-S-RO3234567--ReportingEvent-33</v>
       </c>
     </row>
@@ -718,12 +728,12 @@
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="5"/>
+      <c r="E7" s="8"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="6" t="str" cm="1">
-        <f t="array" ref="H7">IF(B7&lt;&gt;"","AEGIS-"&amp;_xlfn.SWITCH(C7,"DEV","ZDEV","VAL","ZVAL","PRD","PRD","?")&amp;"-"&amp;_xlfn.SWITCH(D7,"Study","S","Molecule","M","?")&amp;"-"&amp;E7&amp;"-"&amp;_xlfn.SWITCH(D7,"Study",F7&amp;"-","Molecule","","?")&amp;G7,"")</f>
-        <v>AEGIS-?-?--?</v>
+        <f t="array" ref="H7">IF(B7&lt;&gt;"","AEGIS-"&amp;C7&amp;"-"&amp;_xlfn.SWITCH(D7,"Study","S","Molecule","M","?")&amp;"-"&amp;E7&amp;"-"&amp;_xlfn.SWITCH(D7,"Study",F7&amp;"-","Molecule","","?")&amp;G7,"")</f>
+        <v>AEGIS--?--?</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -737,7 +747,7 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="6" t="str" cm="1">
-        <f t="array" ref="H8">IF(B8&lt;&gt;"","AEGIS-"&amp;_xlfn.SWITCH(C8,"DEV","ZDEV","VAL","ZVAL","PRD","PRD","?")&amp;"-"&amp;_xlfn.SWITCH(D8,"Study","S","Molecule","M","?")&amp;"-"&amp;E8&amp;"-"&amp;_xlfn.SWITCH(D8,"Study",F8&amp;"-","Molecule","","?")&amp;G8,"")</f>
+        <f t="array" ref="H8">IF(B8&lt;&gt;"","AEGIS-"&amp;C8&amp;"-"&amp;_xlfn.SWITCH(D8,"Study","S","Molecule","M","?")&amp;"-"&amp;E8&amp;"-"&amp;_xlfn.SWITCH(D8,"Study",F8&amp;"-","Molecule","","?")&amp;G8,"")</f>
         <v/>
       </c>
     </row>
@@ -752,7 +762,7 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="6" t="str" cm="1">
-        <f t="array" ref="H9">IF(B9&lt;&gt;"","AEGIS-"&amp;_xlfn.SWITCH(C9,"DEV","ZDEV","VAL","ZVAL","PRD","PRD","?")&amp;"-"&amp;_xlfn.SWITCH(D9,"Study","S","Molecule","M","?")&amp;"-"&amp;E9&amp;"-"&amp;_xlfn.SWITCH(D9,"Study",F9&amp;"-","Molecule","","?")&amp;G9,"")</f>
+        <f t="array" ref="H9">IF(B9&lt;&gt;"","AEGIS-"&amp;C9&amp;"-"&amp;_xlfn.SWITCH(D9,"Study","S","Molecule","M","?")&amp;"-"&amp;E9&amp;"-"&amp;_xlfn.SWITCH(D9,"Study",F9&amp;"-","Molecule","","?")&amp;G9,"")</f>
         <v/>
       </c>
     </row>
@@ -767,7 +777,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="6" t="str" cm="1">
-        <f t="array" ref="H10">IF(B10&lt;&gt;"","AEGIS-"&amp;_xlfn.SWITCH(C10,"DEV","ZDEV","VAL","ZVAL","PRD","PRD","?")&amp;"-"&amp;_xlfn.SWITCH(D10,"Study","S","Molecule","M","?")&amp;"-"&amp;E10&amp;"-"&amp;_xlfn.SWITCH(D10,"Study",F10&amp;"-","Molecule","","?")&amp;G10,"")</f>
+        <f t="array" ref="H10">IF(B10&lt;&gt;"","AEGIS-"&amp;C10&amp;"-"&amp;_xlfn.SWITCH(D10,"Study","S","Molecule","M","?")&amp;"-"&amp;E10&amp;"-"&amp;_xlfn.SWITCH(D10,"Study",F10&amp;"-","Molecule","","?")&amp;G10,"")</f>
         <v/>
       </c>
     </row>
@@ -782,7 +792,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="6" t="str" cm="1">
-        <f t="array" ref="H11">IF(B11&lt;&gt;"","AEGIS-"&amp;_xlfn.SWITCH(C11,"DEV","ZDEV","VAL","ZVAL","PRD","PRD","?")&amp;"-"&amp;_xlfn.SWITCH(D11,"Study","S","Molecule","M","?")&amp;"-"&amp;E11&amp;"-"&amp;_xlfn.SWITCH(D11,"Study",F11&amp;"-","Molecule","","?")&amp;G11,"")</f>
+        <f t="array" ref="H11">IF(B11&lt;&gt;"","AEGIS-"&amp;C11&amp;"-"&amp;_xlfn.SWITCH(D11,"Study","S","Molecule","M","?")&amp;"-"&amp;E11&amp;"-"&amp;_xlfn.SWITCH(D11,"Study",F11&amp;"-","Molecule","","?")&amp;G11,"")</f>
         <v/>
       </c>
     </row>
@@ -797,7 +807,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="6" t="str" cm="1">
-        <f t="array" ref="H12">IF(B12&lt;&gt;"","AEGIS-"&amp;_xlfn.SWITCH(C12,"DEV","ZDEV","VAL","ZVAL","PRD","PRD","?")&amp;"-"&amp;_xlfn.SWITCH(D12,"Study","S","Molecule","M","?")&amp;"-"&amp;E12&amp;"-"&amp;_xlfn.SWITCH(D12,"Study",F12&amp;"-","Molecule","","?")&amp;G12,"")</f>
+        <f t="array" ref="H12">IF(B12&lt;&gt;"","AEGIS-"&amp;C12&amp;"-"&amp;_xlfn.SWITCH(D12,"Study","S","Molecule","M","?")&amp;"-"&amp;E12&amp;"-"&amp;_xlfn.SWITCH(D12,"Study",F12&amp;"-","Molecule","","?")&amp;G12,"")</f>
         <v/>
       </c>
     </row>
@@ -812,7 +822,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="6" t="str" cm="1">
-        <f t="array" ref="H13">IF(B13&lt;&gt;"","AEGIS-"&amp;_xlfn.SWITCH(C13,"DEV","ZDEV","VAL","ZVAL","PRD","PRD","?")&amp;"-"&amp;_xlfn.SWITCH(D13,"Study","S","Molecule","M","?")&amp;"-"&amp;E13&amp;"-"&amp;_xlfn.SWITCH(D13,"Study",F13&amp;"-","Molecule","","?")&amp;G13,"")</f>
+        <f t="array" ref="H13">IF(B13&lt;&gt;"","AEGIS-"&amp;C13&amp;"-"&amp;_xlfn.SWITCH(D13,"Study","S","Molecule","M","?")&amp;"-"&amp;E13&amp;"-"&amp;_xlfn.SWITCH(D13,"Study",F13&amp;"-","Molecule","","?")&amp;G13,"")</f>
         <v/>
       </c>
     </row>

--- a/NewRepoInfo.xlsx
+++ b/NewRepoInfo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\00.Work\00.GitData\R_Repo_Factory_202603\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F388420A-534F-45A7-ADE7-87D7AF85ABB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DFDDB9E-4CFA-4675-9D5D-AA4D2463F387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C9434CED-3E06-4E35-AD4B-02AAE4ABB6B6}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -164,6 +164,10 @@
   </si>
   <si>
     <t>ReportingEvent-33</t>
+  </si>
+  <si>
+    <t>STD-0003</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -710,22 +714,22 @@
       <c r="E6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="5"/>
+      <c r="F6" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="G6" s="5" t="s">
         <v>25</v>
       </c>
       <c r="H6" s="6" t="str" cm="1">
         <f t="array" ref="H6">IF(B6&lt;&gt;"","AEGIS-"&amp;C6&amp;"-"&amp;_xlfn.SWITCH(D6,"Study","S","Molecule","M","?")&amp;"-"&amp;E6&amp;"-"&amp;_xlfn.SWITCH(D6,"Study",F6&amp;"-","Molecule","","?")&amp;G6,"")</f>
-        <v>AEGIS-PRD-S-RO3234567--ReportingEvent-33</v>
+        <v>AEGIS-PRD-S-RO3234567-STD-0003-ReportingEvent-33</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="B7" s="5"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="8"/>
@@ -733,7 +737,7 @@
       <c r="G7" s="5"/>
       <c r="H7" s="6" t="str" cm="1">
         <f t="array" ref="H7">IF(B7&lt;&gt;"","AEGIS-"&amp;C7&amp;"-"&amp;_xlfn.SWITCH(D7,"Study","S","Molecule","M","?")&amp;"-"&amp;E7&amp;"-"&amp;_xlfn.SWITCH(D7,"Study",F7&amp;"-","Molecule","","?")&amp;G7,"")</f>
-        <v>AEGIS--?--?</v>
+        <v/>
       </c>
     </row>
     <row r="8" spans="1:8">
